--- a/Cleveland_Cavaliers_2025-26_stats.xlsx
+++ b/Cleveland_Cavaliers_2025-26_stats.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1262,6 +1262,63 @@
       </c>
       <c r="Q14" t="n">
         <v>31</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>9</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>22</v>
+      </c>
+      <c r="F15" t="n">
+        <v>13</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2</v>
+      </c>
+      <c r="N15" t="n">
+        <v>16</v>
+      </c>
+      <c r="O15" t="n">
+        <v>4</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1275,7 +1332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2104,6 +2161,63 @@
       </c>
       <c r="Q14" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2117,7 +2231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2946,6 +3060,63 @@
       </c>
       <c r="Q14" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>7</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>13</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>4</v>
+      </c>
+      <c r="N15" t="n">
+        <v>6</v>
+      </c>
+      <c r="O15" t="n">
+        <v>4</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2959,7 +3130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3788,6 +3959,63 @@
       </c>
       <c r="Q14" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -3823,7 +4051,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.45454545454545</v>
+        <v>30.41666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -3833,7 +4061,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>19.23076923076923</v>
       </c>
     </row>
     <row r="4">
@@ -3843,7 +4071,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -3853,7 +4081,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.54545454545454</v>
+        <v>15.58333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -3863,7 +4091,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13.4</v>
+        <v>13.36363636363636</v>
       </c>
     </row>
     <row r="7">
@@ -3893,7 +4121,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -3903,27 +4131,27 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.1</v>
+        <v>6.363636363636363</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Craig Porter Jr.</t>
+          <t>Dean Wade</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.692307692307693</v>
+        <v>5.538461538461538</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dean Wade</t>
+          <t>Craig Porter Jr.</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.666666666666667</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13">
@@ -3933,7 +4161,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.454545454545454</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -3943,7 +4171,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>3.666666666666667</v>
       </c>
     </row>
     <row r="15">
@@ -3999,7 +4227,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.454545454545454</v>
+        <v>5.416666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -4009,7 +4237,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.4</v>
+        <v>5.363636363636363</v>
       </c>
     </row>
     <row r="4">
@@ -4029,7 +4257,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.166666666666667</v>
+        <v>4.153846153846154</v>
       </c>
     </row>
     <row r="6">
@@ -4039,7 +4267,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.1</v>
+        <v>3.090909090909091</v>
       </c>
     </row>
     <row r="7">
@@ -4049,7 +4277,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.769230769230769</v>
+        <v>2.642857142857143</v>
       </c>
     </row>
     <row r="8">
@@ -4059,7 +4287,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.6</v>
+        <v>2.454545454545455</v>
       </c>
     </row>
     <row r="9">
@@ -4079,7 +4307,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.727272727272727</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="11">
@@ -4089,27 +4317,27 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.454545454545455</v>
+        <v>1.333333333333333</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Tyrese Proctor</t>
+          <t>Dean Wade</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.272727272727273</v>
+        <v>1.307692307692308</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dean Wade</t>
+          <t>Tyrese Proctor</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.25</v>
+        <v>1.166666666666667</v>
       </c>
     </row>
     <row r="14">
@@ -4129,7 +4357,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="16">
@@ -4175,7 +4403,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.666666666666666</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -4185,7 +4413,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.909090909090909</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="4">
@@ -4195,7 +4423,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.9</v>
+        <v>4.727272727272728</v>
       </c>
     </row>
     <row r="5">
@@ -4205,13 +4433,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.545454545454546</v>
+        <v>4.583333333333333</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jaylon Tyson</t>
+          <t>Lonzo Ball</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -4221,11 +4449,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lonzo Ball</t>
+          <t>Jaylon Tyson</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -4235,27 +4463,27 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Larry Nance Jr.</t>
+          <t>Dean Wade</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.454545454545455</v>
+        <v>3.384615384615385</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dean Wade</t>
+          <t>Larry Nance Jr.</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.333333333333333</v>
+        <v>3.166666666666667</v>
       </c>
     </row>
     <row r="11">
@@ -4275,7 +4503,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.923076923076923</v>
+        <v>2.928571428571428</v>
       </c>
     </row>
     <row r="13">
@@ -4305,7 +4533,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.6</v>
+        <v>1.818181818181818</v>
       </c>
     </row>
     <row r="16">
@@ -4315,7 +4543,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.090909090909091</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4361,7 +4589,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.6</v>
+        <v>3.454545454545455</v>
       </c>
     </row>
     <row r="4">
@@ -4391,7 +4619,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1.909090909090909</v>
       </c>
     </row>
     <row r="7">
@@ -4401,7 +4629,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.666666666666667</v>
+        <v>1.769230769230769</v>
       </c>
     </row>
     <row r="8">
@@ -4411,7 +4639,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.5</v>
+        <v>1.636363636363636</v>
       </c>
     </row>
     <row r="9">
@@ -4421,7 +4649,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.25</v>
+        <v>1.153846153846154</v>
       </c>
     </row>
     <row r="10">
@@ -4431,7 +4659,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.090909090909091</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -4441,7 +4669,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.7857142857142857</v>
       </c>
     </row>
     <row r="12">
@@ -4451,7 +4679,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="13">
@@ -4505,7 +4733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4808,6 +5036,27 @@
         <v>239</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>108</v>
+      </c>
+      <c r="D15" t="n">
+        <v>100</v>
+      </c>
+      <c r="E15" t="n">
+        <v>208</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
